--- a/artfynd/A 57617-2025 artfynd.xlsx
+++ b/artfynd/A 57617-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127803784</v>
+        <v>127803786</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517307</v>
+        <v>517227</v>
       </c>
       <c r="R2" t="n">
-        <v>6946839</v>
+        <v>6946983</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127803785</v>
+        <v>127803784</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517058</v>
+        <v>517307</v>
       </c>
       <c r="R3" t="n">
-        <v>6946797</v>
+        <v>6946839</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,37 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127803786</v>
+        <v>127803785</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517227</v>
+        <v>517058</v>
       </c>
       <c r="R4" t="n">
-        <v>6946983</v>
+        <v>6946797</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 57617-2025 artfynd.xlsx
+++ b/artfynd/A 57617-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803786</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803784</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127803785</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>